--- a/currentbuild/all-profiles.xlsx
+++ b/currentbuild/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.1</t>
+    <t>1.3.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/currentbuild/all-profiles.xlsx
+++ b/currentbuild/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.0</t>
+    <t>1.4.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/currentbuild/all-profiles.xlsx
+++ b/currentbuild/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3680" uniqueCount="576">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4135" uniqueCount="609">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.4.1</t>
+    <t>1.4.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -669,7 +669,7 @@
 </t>
   </si>
   <si>
-    <t>open</t>
+    <t>closed</t>
   </si>
   <si>
     <t>Observation.effective[x]:effectiveDateTime</t>
@@ -682,13 +682,39 @@
 </t>
   </si>
   <si>
-    <t>Observation.issued</t>
+    <t>Observation.effective[x]:effectivePeriod</t>
+  </si>
+  <si>
+    <t>effectivePeriod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Observation.effective[x]:effectiveTiming</t>
+  </si>
+  <si>
+    <t>effectiveTiming</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Timing
+</t>
+  </si>
+  <si>
+    <t>Observation.effective[x]:effectiveInstant</t>
+  </si>
+  <si>
+    <t>effectiveInstant</t>
   </si>
   <si>
     <t xml:space="preserve">instant
 </t>
   </si>
   <si>
+    <t>Observation.issued</t>
+  </si>
+  <si>
     <t>Date/Time this version was made available</t>
   </si>
   <si>
@@ -747,6 +773,94 @@
 </t>
   </si>
   <si>
+    <t>Observation.value[x]:valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueString</t>
+  </si>
+  <si>
+    <t>valueString</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueBoolean</t>
+  </si>
+  <si>
+    <t>valueBoolean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueInteger</t>
+  </si>
+  <si>
+    <t>valueInteger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">integer
+</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueRange</t>
+  </si>
+  <si>
+    <t>valueRange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Range
+</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueRatio</t>
+  </si>
+  <si>
+    <t>valueRatio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ratio
+</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueSampledData</t>
+  </si>
+  <si>
+    <t>valueSampledData</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SampledData
+</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueTime</t>
+  </si>
+  <si>
+    <t>valueTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">time
+</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueDateTime</t>
+  </si>
+  <si>
+    <t>valueDateTime</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valuePeriod</t>
+  </si>
+  <si>
+    <t>valuePeriod</t>
+  </si>
+  <si>
     <t>Observation.dataAbsentReason</t>
   </si>
   <si>
@@ -918,10 +1032,6 @@
     <t>Observation.referenceRange.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
     <t>Unique id for inter-element referencing</t>
   </si>
   <si>
@@ -974,6 +1084,10 @@
 </t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
+  </si>
+  <si>
     <t>Observation.referenceRange.high</t>
   </si>
   <si>
@@ -1026,10 +1140,6 @@
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Range
-</t>
   </si>
   <si>
     <t>Applicable age range, if relevant</t>
@@ -1227,10 +1337,6 @@
   </si>
   <si>
     <t>Patient.active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
   </si>
   <si>
     <t>Whether this patient's record is in active use</t>
@@ -1283,6 +1389,9 @@
     <t>Extensions are always sliced by (at least) url</t>
   </si>
   <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>Patient.name.use</t>
   </si>
   <si>
@@ -1388,10 +1497,6 @@
   </si>
   <si>
     <t>Patient.name.period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
-</t>
   </si>
   <si>
     <t>Time period when name was/is in use</t>
@@ -2140,7 +2245,7 @@
         <v>2</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>361</v>
+        <v>395</v>
       </c>
     </row>
     <row r="24">
@@ -2148,7 +2253,7 @@
         <v>4</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>362</v>
+        <v>396</v>
       </c>
     </row>
     <row r="25">
@@ -2164,7 +2269,7 @@
         <v>8</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>363</v>
+        <v>397</v>
       </c>
     </row>
     <row r="27">
@@ -2172,7 +2277,7 @@
         <v>10</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>364</v>
+        <v>398</v>
       </c>
     </row>
     <row r="28">
@@ -2194,7 +2299,7 @@
         <v>15</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>365</v>
+        <v>399</v>
       </c>
     </row>
     <row r="31">
@@ -2226,7 +2331,7 @@
         <v>23</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>366</v>
+        <v>400</v>
       </c>
     </row>
     <row r="35">
@@ -2262,7 +2367,7 @@
         <v>31</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>367</v>
+        <v>401</v>
       </c>
     </row>
     <row r="40">
@@ -2270,7 +2375,7 @@
         <v>33</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>368</v>
+        <v>402</v>
       </c>
     </row>
     <row r="41">
@@ -2296,13 +2401,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK107"/>
+  <dimension ref="A1:AK120"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.15234375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="38.30078125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="15.40234375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="19.078125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="34.21875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -4571,11 +4676,13 @@
         <v>212</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="D22" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="D22" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="E22" t="s" s="2">
-        <v>78</v>
+        <v>201</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" t="s" s="2">
@@ -4594,18 +4701,20 @@
         <v>86</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="P22" s="2"/>
+        <v>205</v>
+      </c>
+      <c r="P22" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="Q22" t="s" s="2">
         <v>78</v>
       </c>
@@ -4653,7 +4762,7 @@
         <v>78</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>76</v>
@@ -4673,21 +4782,23 @@
         <v>3</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="D23" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="D23" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="E23" t="s" s="2">
-        <v>78</v>
+        <v>201</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>78</v>
@@ -4699,17 +4810,19 @@
         <v>86</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>204</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="P23" t="s" s="2">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="Q23" t="s" s="2">
         <v>78</v>
@@ -4758,13 +4871,13 @@
         <v>78</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>217</v>
+        <v>200</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>78</v>
@@ -4778,14 +4891,16 @@
         <v>3</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="D24" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="D24" t="s" s="2">
+        <v>219</v>
+      </c>
       <c r="E24" t="s" s="2">
-        <v>78</v>
+        <v>201</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" t="s" s="2">
@@ -4804,19 +4919,19 @@
         <v>86</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>225</v>
+        <v>204</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>226</v>
+        <v>205</v>
       </c>
       <c r="P24" t="s" s="2">
-        <v>227</v>
+        <v>206</v>
       </c>
       <c r="Q24" t="s" s="2">
         <v>78</v>
@@ -4853,17 +4968,19 @@
         <v>78</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="AD24" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AE24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>208</v>
+        <v>78</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>76</v>
@@ -4872,7 +4989,7 @@
         <v>85</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>228</v>
+        <v>78</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>97</v>
@@ -4883,14 +5000,12 @@
         <v>3</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="D25" t="s" s="2">
-        <v>230</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="D25" s="2"/>
       <c r="E25" t="s" s="2">
         <v>78</v>
       </c>
@@ -4902,7 +5017,7 @@
         <v>85</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J25" t="s" s="2">
         <v>78</v>
@@ -4911,20 +5026,18 @@
         <v>86</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="M25" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="O25" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="N25" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="P25" t="s" s="2">
-        <v>227</v>
-      </c>
+      <c r="P25" s="2"/>
       <c r="Q25" t="s" s="2">
         <v>78</v>
       </c>
@@ -4972,7 +5085,7 @@
         <v>78</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>76</v>
@@ -4981,7 +5094,7 @@
         <v>85</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>228</v>
+        <v>78</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>97</v>
@@ -4992,10 +5105,10 @@
         <v>3</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" t="s" s="2">
@@ -5006,7 +5119,7 @@
         <v>76</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>78</v>
@@ -5015,22 +5128,20 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>166</v>
+        <v>226</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>235</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="Q26" t="s" s="2">
         <v>78</v>
@@ -5055,13 +5166,13 @@
         <v>78</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>237</v>
+        <v>78</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>238</v>
+        <v>78</v>
       </c>
       <c r="AA26" t="s" s="2">
-        <v>239</v>
+        <v>78</v>
       </c>
       <c r="AB26" t="s" s="2">
         <v>78</v>
@@ -5079,16 +5190,16 @@
         <v>78</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>240</v>
+        <v>78</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>97</v>
@@ -5099,21 +5210,21 @@
         <v>3</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" t="s" s="2">
-        <v>242</v>
+        <v>78</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>78</v>
@@ -5122,22 +5233,22 @@
         <v>78</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>166</v>
+        <v>231</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="P27" t="s" s="2">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="Q27" t="s" s="2">
         <v>78</v>
@@ -5162,40 +5273,38 @@
         <v>78</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>237</v>
+        <v>78</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>247</v>
+        <v>78</v>
       </c>
       <c r="AA27" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="AB27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="AD27" s="2"/>
       <c r="AE27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>78</v>
+        <v>208</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>78</v>
+        <v>236</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>97</v>
@@ -5206,12 +5315,14 @@
         <v>3</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="D28" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="D28" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="E28" t="s" s="2">
         <v>78</v>
       </c>
@@ -5220,31 +5331,31 @@
         <v>76</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>251</v>
+        <v>232</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>252</v>
+        <v>233</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>253</v>
+        <v>234</v>
       </c>
       <c r="P28" t="s" s="2">
-        <v>254</v>
+        <v>235</v>
       </c>
       <c r="Q28" t="s" s="2">
         <v>78</v>
@@ -5293,16 +5404,16 @@
         <v>78</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>249</v>
+        <v>230</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>78</v>
+        <v>236</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>97</v>
@@ -5313,12 +5424,14 @@
         <v>3</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="D29" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="D29" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="E29" t="s" s="2">
         <v>78</v>
       </c>
@@ -5336,21 +5449,23 @@
         <v>78</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>166</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>256</v>
+        <v>232</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>257</v>
+        <v>233</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="P29" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="P29" t="s" s="2">
+        <v>235</v>
+      </c>
       <c r="Q29" t="s" s="2">
         <v>78</v>
       </c>
@@ -5374,13 +5489,13 @@
         <v>78</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>179</v>
+        <v>78</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>259</v>
+        <v>78</v>
       </c>
       <c r="AA29" t="s" s="2">
-        <v>260</v>
+        <v>78</v>
       </c>
       <c r="AB29" t="s" s="2">
         <v>78</v>
@@ -5398,7 +5513,7 @@
         <v>78</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>255</v>
+        <v>230</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>76</v>
@@ -5407,7 +5522,7 @@
         <v>85</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>78</v>
+        <v>236</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>97</v>
@@ -5418,12 +5533,14 @@
         <v>3</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>261</v>
+        <v>242</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="D30" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="D30" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="E30" t="s" s="2">
         <v>78</v>
       </c>
@@ -5441,22 +5558,22 @@
         <v>78</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>166</v>
+        <v>244</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>263</v>
+        <v>233</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>264</v>
+        <v>234</v>
       </c>
       <c r="P30" t="s" s="2">
-        <v>265</v>
+        <v>235</v>
       </c>
       <c r="Q30" t="s" s="2">
         <v>78</v>
@@ -5481,13 +5598,13 @@
         <v>78</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>179</v>
+        <v>78</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>266</v>
+        <v>78</v>
       </c>
       <c r="AA30" t="s" s="2">
-        <v>267</v>
+        <v>78</v>
       </c>
       <c r="AB30" t="s" s="2">
         <v>78</v>
@@ -5505,7 +5622,7 @@
         <v>78</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>261</v>
+        <v>230</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>76</v>
@@ -5514,7 +5631,7 @@
         <v>85</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>78</v>
+        <v>236</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>97</v>
@@ -5525,12 +5642,14 @@
         <v>3</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>268</v>
+        <v>245</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="D31" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="D31" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="E31" t="s" s="2">
         <v>78</v>
       </c>
@@ -5548,21 +5667,23 @@
         <v>78</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>270</v>
+        <v>232</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>271</v>
+        <v>233</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="P31" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="P31" t="s" s="2">
+        <v>235</v>
+      </c>
       <c r="Q31" t="s" s="2">
         <v>78</v>
       </c>
@@ -5610,7 +5731,7 @@
         <v>78</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>268</v>
+        <v>230</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>76</v>
@@ -5619,7 +5740,7 @@
         <v>85</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>78</v>
+        <v>236</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>97</v>
@@ -5630,12 +5751,14 @@
         <v>3</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>273</v>
+        <v>248</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="D32" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="D32" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="E32" t="s" s="2">
         <v>78</v>
       </c>
@@ -5653,21 +5776,23 @@
         <v>78</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>274</v>
+        <v>250</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>275</v>
+        <v>232</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>276</v>
+        <v>233</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="P32" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="P32" t="s" s="2">
+        <v>235</v>
+      </c>
       <c r="Q32" t="s" s="2">
         <v>78</v>
       </c>
@@ -5715,7 +5840,7 @@
         <v>78</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>273</v>
+        <v>230</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>76</v>
@@ -5724,7 +5849,7 @@
         <v>85</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>78</v>
+        <v>236</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>97</v>
@@ -5735,12 +5860,14 @@
         <v>3</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="D33" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="D33" t="s" s="2">
+        <v>252</v>
+      </c>
       <c r="E33" t="s" s="2">
         <v>78</v>
       </c>
@@ -5749,7 +5876,7 @@
         <v>76</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>78</v>
@@ -5758,22 +5885,22 @@
         <v>78</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>279</v>
+        <v>253</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>280</v>
+        <v>232</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>281</v>
+        <v>233</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>282</v>
+        <v>234</v>
       </c>
       <c r="P33" t="s" s="2">
-        <v>283</v>
+        <v>235</v>
       </c>
       <c r="Q33" t="s" s="2">
         <v>78</v>
@@ -5822,19 +5949,19 @@
         <v>78</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>278</v>
+        <v>230</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>78</v>
+        <v>236</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>284</v>
+        <v>97</v>
       </c>
     </row>
     <row r="34">
@@ -5842,12 +5969,14 @@
         <v>3</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>285</v>
+        <v>254</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="D34" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="D34" t="s" s="2">
+        <v>255</v>
+      </c>
       <c r="E34" t="s" s="2">
         <v>78</v>
       </c>
@@ -5865,19 +5994,23 @@
         <v>78</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>286</v>
+        <v>256</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>287</v>
+        <v>232</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="O34" s="2"/>
-      <c r="P34" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="P34" t="s" s="2">
+        <v>235</v>
+      </c>
       <c r="Q34" t="s" s="2">
         <v>78</v>
       </c>
@@ -5925,7 +6058,7 @@
         <v>78</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>289</v>
+        <v>230</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>76</v>
@@ -5934,10 +6067,10 @@
         <v>85</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>78</v>
+        <v>236</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
     </row>
     <row r="35">
@@ -5945,21 +6078,23 @@
         <v>3</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>290</v>
+        <v>257</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="D35" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="D35" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="E35" t="s" s="2">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>78</v>
@@ -5968,21 +6103,23 @@
         <v>78</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>129</v>
+        <v>259</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>130</v>
+        <v>232</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>291</v>
+        <v>233</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="P35" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="P35" t="s" s="2">
+        <v>235</v>
+      </c>
       <c r="Q35" t="s" s="2">
         <v>78</v>
       </c>
@@ -6030,19 +6167,19 @@
         <v>78</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>292</v>
+        <v>230</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>78</v>
+        <v>236</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>134</v>
+        <v>97</v>
       </c>
     </row>
     <row r="36">
@@ -6050,45 +6187,47 @@
         <v>3</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>293</v>
+        <v>260</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="D36" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="D36" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="E36" t="s" s="2">
-        <v>294</v>
+        <v>78</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="K36" t="s" s="2">
         <v>86</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>129</v>
+        <v>262</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>295</v>
+        <v>232</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>296</v>
+        <v>233</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>132</v>
+        <v>234</v>
       </c>
       <c r="P36" t="s" s="2">
-        <v>138</v>
+        <v>235</v>
       </c>
       <c r="Q36" t="s" s="2">
         <v>78</v>
@@ -6137,19 +6276,19 @@
         <v>78</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>297</v>
+        <v>230</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>78</v>
+        <v>236</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>134</v>
+        <v>97</v>
       </c>
     </row>
     <row r="37">
@@ -6157,12 +6296,14 @@
         <v>3</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>298</v>
+        <v>263</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="D37" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="D37" t="s" s="2">
+        <v>264</v>
+      </c>
       <c r="E37" t="s" s="2">
         <v>78</v>
       </c>
@@ -6180,19 +6321,23 @@
         <v>78</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>299</v>
+        <v>211</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>300</v>
+        <v>232</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="O37" s="2"/>
-      <c r="P37" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="P37" t="s" s="2">
+        <v>235</v>
+      </c>
       <c r="Q37" t="s" s="2">
         <v>78</v>
       </c>
@@ -6240,7 +6385,7 @@
         <v>78</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>298</v>
+        <v>230</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>76</v>
@@ -6249,7 +6394,7 @@
         <v>85</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>302</v>
+        <v>236</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>97</v>
@@ -6260,12 +6405,14 @@
         <v>3</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>303</v>
+        <v>265</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="D38" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="D38" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="E38" t="s" s="2">
         <v>78</v>
       </c>
@@ -6283,19 +6430,23 @@
         <v>78</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>299</v>
+        <v>214</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>304</v>
+        <v>232</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="O38" s="2"/>
-      <c r="P38" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="P38" t="s" s="2">
+        <v>235</v>
+      </c>
       <c r="Q38" t="s" s="2">
         <v>78</v>
       </c>
@@ -6343,7 +6494,7 @@
         <v>78</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>303</v>
+        <v>230</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>76</v>
@@ -6352,7 +6503,7 @@
         <v>85</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>302</v>
+        <v>236</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>97</v>
@@ -6363,10 +6514,10 @@
         <v>3</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>306</v>
+        <v>267</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>306</v>
+        <v>267</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" t="s" s="2">
@@ -6392,16 +6543,16 @@
         <v>166</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>307</v>
+        <v>268</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>308</v>
+        <v>269</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>309</v>
+        <v>270</v>
       </c>
       <c r="P39" t="s" s="2">
-        <v>310</v>
+        <v>271</v>
       </c>
       <c r="Q39" t="s" s="2">
         <v>78</v>
@@ -6426,13 +6577,13 @@
         <v>78</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>109</v>
+        <v>272</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>311</v>
+        <v>273</v>
       </c>
       <c r="AA39" t="s" s="2">
-        <v>312</v>
+        <v>274</v>
       </c>
       <c r="AB39" t="s" s="2">
         <v>78</v>
@@ -6450,7 +6601,7 @@
         <v>78</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>306</v>
+        <v>267</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>76</v>
@@ -6459,7 +6610,7 @@
         <v>85</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>78</v>
+        <v>275</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>97</v>
@@ -6470,14 +6621,14 @@
         <v>3</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>313</v>
+        <v>276</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>313</v>
+        <v>276</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" t="s" s="2">
-        <v>78</v>
+        <v>277</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" t="s" s="2">
@@ -6499,16 +6650,16 @@
         <v>166</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>314</v>
+        <v>278</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>315</v>
+        <v>279</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>316</v>
+        <v>280</v>
       </c>
       <c r="P40" t="s" s="2">
-        <v>317</v>
+        <v>281</v>
       </c>
       <c r="Q40" t="s" s="2">
         <v>78</v>
@@ -6533,13 +6684,13 @@
         <v>78</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>179</v>
+        <v>272</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>318</v>
+        <v>282</v>
       </c>
       <c r="AA40" t="s" s="2">
-        <v>319</v>
+        <v>283</v>
       </c>
       <c r="AB40" t="s" s="2">
         <v>78</v>
@@ -6557,7 +6708,7 @@
         <v>78</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>313</v>
+        <v>276</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>76</v>
@@ -6577,10 +6728,10 @@
         <v>3</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>320</v>
+        <v>284</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>320</v>
+        <v>284</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
@@ -6591,7 +6742,7 @@
         <v>76</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>78</v>
@@ -6603,17 +6754,19 @@
         <v>78</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>321</v>
+        <v>285</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>322</v>
+        <v>286</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>287</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="P41" t="s" s="2">
-        <v>324</v>
+        <v>289</v>
       </c>
       <c r="Q41" t="s" s="2">
         <v>78</v>
@@ -6662,13 +6815,13 @@
         <v>78</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>320</v>
+        <v>284</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>78</v>
@@ -6682,10 +6835,10 @@
         <v>3</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>325</v>
+        <v>290</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>325</v>
+        <v>290</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
@@ -6708,15 +6861,17 @@
         <v>78</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>286</v>
+        <v>166</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>326</v>
+        <v>291</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>292</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="P42" s="2"/>
       <c r="Q42" t="s" s="2">
         <v>78</v>
@@ -6741,13 +6896,13 @@
         <v>78</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>78</v>
+        <v>294</v>
       </c>
       <c r="AA42" t="s" s="2">
-        <v>78</v>
+        <v>295</v>
       </c>
       <c r="AB42" t="s" s="2">
         <v>78</v>
@@ -6765,7 +6920,7 @@
         <v>78</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>325</v>
+        <v>290</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>76</v>
@@ -6785,10 +6940,10 @@
         <v>3</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>328</v>
+        <v>296</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>328</v>
+        <v>296</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" t="s" s="2">
@@ -6799,7 +6954,7 @@
         <v>76</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>78</v>
@@ -6808,21 +6963,23 @@
         <v>78</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>329</v>
+        <v>166</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>330</v>
+        <v>297</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>331</v>
+        <v>298</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="P43" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="P43" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="Q43" t="s" s="2">
         <v>78</v>
       </c>
@@ -6846,13 +7003,13 @@
         <v>78</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>78</v>
+        <v>301</v>
       </c>
       <c r="AA43" t="s" s="2">
-        <v>78</v>
+        <v>302</v>
       </c>
       <c r="AB43" t="s" s="2">
         <v>78</v>
@@ -6870,13 +7027,13 @@
         <v>78</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>328</v>
+        <v>296</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>78</v>
@@ -6890,10 +7047,10 @@
         <v>3</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>333</v>
+        <v>303</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>333</v>
+        <v>303</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" t="s" s="2">
@@ -6904,7 +7061,7 @@
         <v>76</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>78</v>
@@ -6913,19 +7070,19 @@
         <v>78</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>334</v>
+        <v>304</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>335</v>
+        <v>305</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>336</v>
+        <v>306</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>337</v>
+        <v>307</v>
       </c>
       <c r="P44" s="2"/>
       <c r="Q44" t="s" s="2">
@@ -6975,13 +7132,13 @@
         <v>78</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>333</v>
+        <v>303</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>78</v>
@@ -6995,10 +7152,10 @@
         <v>3</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>338</v>
+        <v>308</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>338</v>
+        <v>308</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" t="s" s="2">
@@ -7009,7 +7166,7 @@
         <v>76</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>78</v>
@@ -7018,23 +7175,21 @@
         <v>78</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>279</v>
+        <v>309</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>339</v>
+        <v>310</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>340</v>
+        <v>311</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="P45" t="s" s="2">
-        <v>342</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="P45" s="2"/>
       <c r="Q45" t="s" s="2">
         <v>78</v>
       </c>
@@ -7082,13 +7237,13 @@
         <v>78</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>338</v>
+        <v>308</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>78</v>
@@ -7102,10 +7257,10 @@
         <v>3</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>343</v>
+        <v>313</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>343</v>
+        <v>313</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" t="s" s="2">
@@ -7116,7 +7271,7 @@
         <v>76</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>78</v>
@@ -7128,16 +7283,20 @@
         <v>78</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>286</v>
+        <v>314</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>287</v>
+        <v>315</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="O46" s="2"/>
-      <c r="P46" s="2"/>
+        <v>316</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="P46" t="s" s="2">
+        <v>318</v>
+      </c>
       <c r="Q46" t="s" s="2">
         <v>78</v>
       </c>
@@ -7185,19 +7344,19 @@
         <v>78</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>289</v>
+        <v>313</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>78</v>
+        <v>319</v>
       </c>
     </row>
     <row r="47">
@@ -7205,21 +7364,21 @@
         <v>3</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>344</v>
+        <v>320</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>344</v>
+        <v>320</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" t="s" s="2">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="F47" s="2"/>
       <c r="G47" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>78</v>
@@ -7231,17 +7390,15 @@
         <v>78</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>129</v>
+        <v>244</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>130</v>
+        <v>321</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>132</v>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" s="2"/>
       <c r="Q47" t="s" s="2">
         <v>78</v>
@@ -7290,19 +7447,19 @@
         <v>78</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>292</v>
+        <v>323</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
     </row>
     <row r="48">
@@ -7310,14 +7467,14 @@
         <v>3</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>345</v>
+        <v>324</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>345</v>
+        <v>324</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
-        <v>294</v>
+        <v>128</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" t="s" s="2">
@@ -7330,26 +7487,24 @@
         <v>78</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="L48" t="s" s="2">
         <v>129</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>295</v>
+        <v>130</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>296</v>
+        <v>325</v>
       </c>
       <c r="O48" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="P48" t="s" s="2">
-        <v>138</v>
-      </c>
+      <c r="P48" s="2"/>
       <c r="Q48" t="s" s="2">
         <v>78</v>
       </c>
@@ -7397,7 +7552,7 @@
         <v>78</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>297</v>
+        <v>326</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>76</v>
@@ -7417,45 +7572,45 @@
         <v>3</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>346</v>
+        <v>327</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>346</v>
+        <v>327</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
-        <v>78</v>
+        <v>328</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="K49" t="s" s="2">
         <v>86</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>166</v>
+        <v>129</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>347</v>
+        <v>329</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>348</v>
+        <v>330</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>349</v>
+        <v>132</v>
       </c>
       <c r="P49" t="s" s="2">
-        <v>178</v>
+        <v>138</v>
       </c>
       <c r="Q49" t="s" s="2">
         <v>78</v>
@@ -7480,13 +7635,13 @@
         <v>78</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>179</v>
+        <v>78</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>180</v>
+        <v>78</v>
       </c>
       <c r="AA49" t="s" s="2">
-        <v>181</v>
+        <v>78</v>
       </c>
       <c r="AB49" t="s" s="2">
         <v>78</v>
@@ -7504,19 +7659,19 @@
         <v>78</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>97</v>
+        <v>134</v>
       </c>
     </row>
     <row r="50">
@@ -7524,10 +7679,10 @@
         <v>3</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>350</v>
+        <v>332</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>350</v>
+        <v>332</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
@@ -7547,23 +7702,19 @@
         <v>78</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>223</v>
+        <v>333</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>351</v>
+        <v>334</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="P50" t="s" s="2">
-        <v>227</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="O50" s="2"/>
+      <c r="P50" s="2"/>
       <c r="Q50" t="s" s="2">
         <v>78</v>
       </c>
@@ -7611,7 +7762,7 @@
         <v>78</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>350</v>
+        <v>332</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>76</v>
@@ -7620,10 +7771,10 @@
         <v>85</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>78</v>
+        <v>336</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>97</v>
+        <v>337</v>
       </c>
     </row>
     <row r="51">
@@ -7631,10 +7782,10 @@
         <v>3</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" t="s" s="2">
@@ -7657,20 +7808,16 @@
         <v>78</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>166</v>
+        <v>333</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="P51" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="O51" s="2"/>
+      <c r="P51" s="2"/>
       <c r="Q51" t="s" s="2">
         <v>78</v>
       </c>
@@ -7694,13 +7841,13 @@
         <v>78</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>237</v>
+        <v>78</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>238</v>
+        <v>78</v>
       </c>
       <c r="AA51" t="s" s="2">
-        <v>239</v>
+        <v>78</v>
       </c>
       <c r="AB51" t="s" s="2">
         <v>78</v>
@@ -7718,7 +7865,7 @@
         <v>78</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>76</v>
@@ -7727,10 +7874,10 @@
         <v>85</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>240</v>
+        <v>336</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>97</v>
+        <v>337</v>
       </c>
     </row>
     <row r="52">
@@ -7738,21 +7885,21 @@
         <v>3</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>357</v>
+        <v>341</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>357</v>
+        <v>341</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
-        <v>242</v>
+        <v>78</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>78</v>
@@ -7767,16 +7914,16 @@
         <v>166</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>243</v>
+        <v>342</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>244</v>
+        <v>343</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>245</v>
+        <v>344</v>
       </c>
       <c r="P52" t="s" s="2">
-        <v>246</v>
+        <v>345</v>
       </c>
       <c r="Q52" t="s" s="2">
         <v>78</v>
@@ -7801,13 +7948,13 @@
         <v>78</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>237</v>
+        <v>109</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>247</v>
+        <v>346</v>
       </c>
       <c r="AA52" t="s" s="2">
-        <v>248</v>
+        <v>347</v>
       </c>
       <c r="AB52" t="s" s="2">
         <v>78</v>
@@ -7825,13 +7972,13 @@
         <v>78</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>357</v>
+        <v>341</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>78</v>
@@ -7845,10 +7992,10 @@
         <v>3</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s" s="2">
@@ -7871,19 +8018,19 @@
         <v>78</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>79</v>
+        <v>166</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>282</v>
+        <v>351</v>
       </c>
       <c r="P53" t="s" s="2">
-        <v>283</v>
+        <v>352</v>
       </c>
       <c r="Q53" t="s" s="2">
         <v>78</v>
@@ -7908,13 +8055,13 @@
         <v>78</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>78</v>
+        <v>353</v>
       </c>
       <c r="AA53" t="s" s="2">
-        <v>78</v>
+        <v>354</v>
       </c>
       <c r="AB53" t="s" s="2">
         <v>78</v>
@@ -7932,7 +8079,7 @@
         <v>78</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>76</v>
@@ -7949,24 +8096,24 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>361</v>
+        <v>3</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
-        <v>369</v>
+        <v>78</v>
       </c>
       <c r="F54" s="2"/>
       <c r="G54" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>78</v>
@@ -7978,16 +8125,18 @@
         <v>78</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>79</v>
+        <v>253</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>371</v>
+        <v>357</v>
       </c>
       <c r="O54" s="2"/>
-      <c r="P54" s="2"/>
+      <c r="P54" t="s" s="2">
+        <v>358</v>
+      </c>
       <c r="Q54" t="s" s="2">
         <v>78</v>
       </c>
@@ -8035,30 +8184,30 @@
         <v>78</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>372</v>
+        <v>97</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>361</v>
+        <v>3</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>373</v>
+        <v>359</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>373</v>
+        <v>359</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
@@ -8078,20 +8227,18 @@
         <v>78</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>87</v>
+        <v>244</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>88</v>
+        <v>360</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>90</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" s="2"/>
       <c r="Q55" t="s" s="2">
         <v>78</v>
@@ -8140,7 +8287,7 @@
         <v>78</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>91</v>
+        <v>359</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>76</v>
@@ -8152,18 +8299,18 @@
         <v>78</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>361</v>
+        <v>3</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
@@ -8174,7 +8321,7 @@
         <v>76</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>78</v>
@@ -8186,15 +8333,17 @@
         <v>86</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>93</v>
+        <v>363</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>94</v>
+        <v>364</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>365</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>366</v>
+      </c>
       <c r="P56" s="2"/>
       <c r="Q56" t="s" s="2">
         <v>78</v>
@@ -8243,13 +8392,13 @@
         <v>78</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>96</v>
+        <v>362</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>78</v>
@@ -8260,13 +8409,13 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>361</v>
+        <v>3</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
@@ -8277,28 +8426,28 @@
         <v>76</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="K57" t="s" s="2">
         <v>86</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>99</v>
+        <v>368</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>100</v>
+        <v>369</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>101</v>
+        <v>370</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>102</v>
+        <v>371</v>
       </c>
       <c r="P57" s="2"/>
       <c r="Q57" t="s" s="2">
@@ -8348,13 +8497,13 @@
         <v>78</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>103</v>
+        <v>367</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>78</v>
@@ -8365,13 +8514,13 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>361</v>
+        <v>3</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
@@ -8382,7 +8531,7 @@
         <v>76</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>78</v>
@@ -8391,21 +8540,23 @@
         <v>78</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>105</v>
+        <v>314</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>106</v>
+        <v>373</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>107</v>
+        <v>374</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="P58" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="P58" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="Q58" t="s" s="2">
         <v>78</v>
       </c>
@@ -8429,13 +8580,13 @@
         <v>78</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="AA58" t="s" s="2">
-        <v>111</v>
+        <v>78</v>
       </c>
       <c r="AB58" t="s" s="2">
         <v>78</v>
@@ -8453,13 +8604,13 @@
         <v>78</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>112</v>
+        <v>372</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>78</v>
@@ -8470,7 +8621,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>361</v>
+        <v>3</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>377</v>
@@ -8480,7 +8631,7 @@
       </c>
       <c r="D59" s="2"/>
       <c r="E59" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" t="s" s="2">
@@ -8499,17 +8650,15 @@
         <v>78</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>115</v>
+        <v>244</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>116</v>
+        <v>321</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>118</v>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="O59" s="2"/>
       <c r="P59" s="2"/>
       <c r="Q59" t="s" s="2">
         <v>78</v>
@@ -8558,7 +8707,7 @@
         <v>78</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>119</v>
+        <v>323</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>76</v>
@@ -8570,12 +8719,12 @@
         <v>78</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>361</v>
+        <v>3</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>378</v>
@@ -8585,7 +8734,7 @@
       </c>
       <c r="D60" s="2"/>
       <c r="E60" t="s" s="2">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="F60" s="2"/>
       <c r="G60" t="s" s="2">
@@ -8604,16 +8753,16 @@
         <v>78</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>124</v>
+        <v>325</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="P60" s="2"/>
       <c r="Q60" t="s" s="2">
@@ -8663,7 +8812,7 @@
         <v>78</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>126</v>
+        <v>326</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>76</v>
@@ -8675,12 +8824,12 @@
         <v>78</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>361</v>
+        <v>3</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>379</v>
@@ -8690,7 +8839,7 @@
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
-        <v>128</v>
+        <v>328</v>
       </c>
       <c r="F61" s="2"/>
       <c r="G61" t="s" s="2">
@@ -8703,24 +8852,26 @@
         <v>78</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="L61" t="s" s="2">
         <v>129</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>130</v>
+        <v>329</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>131</v>
+        <v>330</v>
       </c>
       <c r="O61" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="P61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="Q61" t="s" s="2">
         <v>78</v>
       </c>
@@ -8768,7 +8919,7 @@
         <v>78</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>133</v>
+        <v>331</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>76</v>
@@ -8785,7 +8936,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>361</v>
+        <v>3</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>380</v>
@@ -8795,38 +8946,38 @@
       </c>
       <c r="D62" s="2"/>
       <c r="E62" t="s" s="2">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K62" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="K62" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="L62" t="s" s="2">
-        <v>129</v>
+        <v>166</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>136</v>
+        <v>381</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>137</v>
+        <v>382</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>132</v>
+        <v>383</v>
       </c>
       <c r="P62" t="s" s="2">
-        <v>138</v>
+        <v>178</v>
       </c>
       <c r="Q62" t="s" s="2">
         <v>78</v>
@@ -8851,13 +9002,13 @@
         <v>78</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="AA62" t="s" s="2">
-        <v>78</v>
+        <v>181</v>
       </c>
       <c r="AB62" t="s" s="2">
         <v>78</v>
@@ -8875,30 +9026,30 @@
         <v>78</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>139</v>
+        <v>380</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>134</v>
+        <v>97</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>361</v>
+        <v>3</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" t="s" s="2">
@@ -8909,10 +9060,10 @@
         <v>76</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J63" t="s" s="2">
         <v>78</v>
@@ -8921,17 +9072,19 @@
         <v>86</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>141</v>
+        <v>231</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="O63" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="P63" t="s" s="2">
-        <v>384</v>
+        <v>235</v>
       </c>
       <c r="Q63" t="s" s="2">
         <v>78</v>
@@ -8980,13 +9133,13 @@
         <v>78</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>78</v>
@@ -8997,13 +9150,13 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>361</v>
+        <v>3</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" t="s" s="2">
@@ -9020,77 +9173,75 @@
         <v>78</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>386</v>
+        <v>166</v>
       </c>
       <c r="M64" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="P64" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="Q64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R64" s="2"/>
+      <c r="S64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG64" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="N64" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="P64" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="Q64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R64" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="S64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>385</v>
-      </c>
       <c r="AH64" t="s" s="2">
         <v>76</v>
       </c>
@@ -9098,7 +9249,7 @@
         <v>85</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>78</v>
+        <v>275</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>97</v>
@@ -9106,17 +9257,17 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>361</v>
+        <v>3</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" t="s" s="2">
-        <v>78</v>
+        <v>277</v>
       </c>
       <c r="F65" s="2"/>
       <c r="G65" t="s" s="2">
@@ -9132,22 +9283,22 @@
         <v>78</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>393</v>
+        <v>166</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>394</v>
+        <v>278</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>395</v>
+        <v>279</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>396</v>
+        <v>280</v>
       </c>
       <c r="P65" t="s" s="2">
-        <v>397</v>
+        <v>281</v>
       </c>
       <c r="Q65" t="s" s="2">
         <v>78</v>
@@ -9172,13 +9323,13 @@
         <v>78</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>78</v>
+        <v>272</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>78</v>
+        <v>282</v>
       </c>
       <c r="AA65" t="s" s="2">
-        <v>78</v>
+        <v>283</v>
       </c>
       <c r="AB65" t="s" s="2">
         <v>78</v>
@@ -9196,7 +9347,7 @@
         <v>78</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AH65" t="s" s="2">
         <v>76</v>
@@ -9213,13 +9364,13 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>361</v>
+        <v>3</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" t="s" s="2">
@@ -9230,7 +9381,7 @@
         <v>76</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>78</v>
@@ -9242,16 +9393,20 @@
         <v>78</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>286</v>
+        <v>79</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>287</v>
+        <v>393</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="O66" s="2"/>
-      <c r="P66" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="P66" t="s" s="2">
+        <v>318</v>
+      </c>
       <c r="Q66" t="s" s="2">
         <v>78</v>
       </c>
@@ -9299,34 +9454,34 @@
         <v>78</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>289</v>
+        <v>392</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" t="s" s="2">
-        <v>128</v>
+        <v>403</v>
       </c>
       <c r="F67" s="2"/>
       <c r="G67" t="s" s="2">
@@ -9345,17 +9500,15 @@
         <v>78</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>129</v>
+        <v>79</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>130</v>
+        <v>404</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>132</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" s="2"/>
       <c r="Q67" t="s" s="2">
         <v>78</v>
@@ -9392,19 +9545,19 @@
         <v>78</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>400</v>
+        <v>78</v>
       </c>
       <c r="AD67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG67" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>76</v>
@@ -9416,18 +9569,18 @@
         <v>78</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>134</v>
+        <v>406</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" t="s" s="2">
@@ -9444,26 +9597,24 @@
         <v>78</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="K68" t="s" s="2">
         <v>86</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>403</v>
+        <v>88</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>404</v>
+        <v>89</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="P68" t="s" s="2">
-        <v>406</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="P68" s="2"/>
       <c r="Q68" t="s" s="2">
         <v>78</v>
       </c>
@@ -9487,13 +9638,13 @@
         <v>78</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>162</v>
+        <v>78</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>407</v>
+        <v>78</v>
       </c>
       <c r="AA68" t="s" s="2">
-        <v>408</v>
+        <v>78</v>
       </c>
       <c r="AB68" t="s" s="2">
         <v>78</v>
@@ -9511,7 +9662,7 @@
         <v>78</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>409</v>
+        <v>91</v>
       </c>
       <c r="AH68" t="s" s="2">
         <v>76</v>
@@ -9523,18 +9674,18 @@
         <v>78</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" t="s" s="2">
@@ -9557,20 +9708,16 @@
         <v>86</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>286</v>
+        <v>93</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>411</v>
+        <v>94</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="P69" t="s" s="2">
-        <v>414</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="O69" s="2"/>
+      <c r="P69" s="2"/>
       <c r="Q69" t="s" s="2">
         <v>78</v>
       </c>
@@ -9618,7 +9765,7 @@
         <v>78</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>415</v>
+        <v>96</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>76</v>
@@ -9635,17 +9782,17 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" t="s" s="2">
-        <v>417</v>
+        <v>78</v>
       </c>
       <c r="F70" s="2"/>
       <c r="G70" t="s" s="2">
@@ -9655,25 +9802,25 @@
         <v>85</v>
       </c>
       <c r="I70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J70" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="J70" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
         <v>86</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>286</v>
+        <v>99</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>418</v>
+        <v>100</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>419</v>
+        <v>101</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>420</v>
+        <v>102</v>
       </c>
       <c r="P70" s="2"/>
       <c r="Q70" t="s" s="2">
@@ -9723,7 +9870,7 @@
         <v>78</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>421</v>
+        <v>103</v>
       </c>
       <c r="AH70" t="s" s="2">
         <v>76</v>
@@ -9740,24 +9887,24 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" t="s" s="2">
-        <v>423</v>
+        <v>78</v>
       </c>
       <c r="F71" s="2"/>
       <c r="G71" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>78</v>
@@ -9766,19 +9913,19 @@
         <v>78</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>286</v>
+        <v>105</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>424</v>
+        <v>106</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>425</v>
+        <v>107</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>426</v>
+        <v>108</v>
       </c>
       <c r="P71" s="2"/>
       <c r="Q71" t="s" s="2">
@@ -9804,13 +9951,13 @@
         <v>78</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="AA71" t="s" s="2">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="AB71" t="s" s="2">
         <v>78</v>
@@ -9828,13 +9975,13 @@
         <v>78</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>427</v>
+        <v>112</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>78</v>
@@ -9845,24 +9992,24 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>428</v>
+        <v>411</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>428</v>
+        <v>411</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="F72" s="2"/>
       <c r="G72" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>78</v>
@@ -9871,18 +10018,20 @@
         <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>286</v>
+        <v>115</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>429</v>
+        <v>116</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="O72" s="2"/>
+        <v>117</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>118</v>
+      </c>
       <c r="P72" s="2"/>
       <c r="Q72" t="s" s="2">
         <v>78</v>
@@ -9931,13 +10080,13 @@
         <v>78</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>431</v>
+        <v>119</v>
       </c>
       <c r="AH72" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>78</v>
@@ -9948,17 +10097,17 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>432</v>
+        <v>412</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>432</v>
+        <v>412</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" t="s" s="2">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" t="s" s="2">
@@ -9974,18 +10123,20 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>286</v>
+        <v>122</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>433</v>
+        <v>123</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="O73" s="2"/>
+        <v>124</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>125</v>
+      </c>
       <c r="P73" s="2"/>
       <c r="Q73" t="s" s="2">
         <v>78</v>
@@ -10034,7 +10185,7 @@
         <v>78</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>435</v>
+        <v>126</v>
       </c>
       <c r="AH73" t="s" s="2">
         <v>76</v>
@@ -10046,29 +10197,29 @@
         <v>78</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>436</v>
+        <v>413</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>436</v>
+        <v>413</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" t="s" s="2">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>78</v>
@@ -10077,21 +10228,21 @@
         <v>78</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>437</v>
+        <v>129</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>438</v>
+        <v>130</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="O74" s="2"/>
-      <c r="P74" t="s" s="2">
-        <v>440</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="P74" s="2"/>
       <c r="Q74" t="s" s="2">
         <v>78</v>
       </c>
@@ -10139,34 +10290,34 @@
         <v>78</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>441</v>
+        <v>133</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>97</v>
+        <v>134</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>442</v>
+        <v>414</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>442</v>
+        <v>414</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="F75" s="2"/>
       <c r="G75" t="s" s="2">
@@ -10179,25 +10330,25 @@
         <v>78</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>443</v>
+        <v>129</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>444</v>
+        <v>136</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>445</v>
+        <v>137</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>446</v>
+        <v>132</v>
       </c>
       <c r="P75" t="s" s="2">
-        <v>447</v>
+        <v>138</v>
       </c>
       <c r="Q75" t="s" s="2">
         <v>78</v>
@@ -10246,7 +10397,7 @@
         <v>78</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>442</v>
+        <v>139</v>
       </c>
       <c r="AH75" t="s" s="2">
         <v>76</v>
@@ -10258,18 +10409,18 @@
         <v>78</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>97</v>
+        <v>134</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>448</v>
+        <v>415</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>448</v>
+        <v>415</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
@@ -10280,10 +10431,10 @@
         <v>76</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J76" t="s" s="2">
         <v>78</v>
@@ -10292,19 +10443,17 @@
         <v>86</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>449</v>
+        <v>416</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>451</v>
-      </c>
+        <v>417</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
-        <v>452</v>
+        <v>418</v>
       </c>
       <c r="Q76" t="s" s="2">
         <v>78</v>
@@ -10329,13 +10478,13 @@
         <v>78</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>162</v>
+        <v>78</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>453</v>
+        <v>78</v>
       </c>
       <c r="AA76" t="s" s="2">
-        <v>454</v>
+        <v>78</v>
       </c>
       <c r="AB76" t="s" s="2">
         <v>78</v>
@@ -10353,13 +10502,13 @@
         <v>78</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>448</v>
+        <v>415</v>
       </c>
       <c r="AH76" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>78</v>
@@ -10370,13 +10519,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>455</v>
+        <v>419</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>455</v>
+        <v>419</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s" s="2">
@@ -10393,30 +10542,32 @@
         <v>78</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="K77" t="s" s="2">
         <v>86</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>456</v>
+        <v>247</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>457</v>
+        <v>420</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>458</v>
+        <v>421</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>459</v>
+        <v>422</v>
       </c>
       <c r="P77" t="s" s="2">
-        <v>460</v>
+        <v>423</v>
       </c>
       <c r="Q77" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="R77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>424</v>
+      </c>
       <c r="S77" t="s" s="2">
         <v>78</v>
       </c>
@@ -10460,7 +10611,7 @@
         <v>78</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>455</v>
+        <v>419</v>
       </c>
       <c r="AH77" t="s" s="2">
         <v>76</v>
@@ -10477,13 +10628,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>461</v>
+        <v>425</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>461</v>
+        <v>425</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
@@ -10494,31 +10645,31 @@
         <v>76</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="K78" t="s" s="2">
         <v>86</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>462</v>
+        <v>426</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>463</v>
+        <v>427</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>464</v>
+        <v>428</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>465</v>
+        <v>429</v>
       </c>
       <c r="P78" t="s" s="2">
-        <v>466</v>
+        <v>430</v>
       </c>
       <c r="Q78" t="s" s="2">
         <v>78</v>
@@ -10567,13 +10718,13 @@
         <v>78</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>461</v>
+        <v>425</v>
       </c>
       <c r="AH78" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>78</v>
@@ -10584,13 +10735,13 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>467</v>
+        <v>431</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>467</v>
+        <v>431</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s" s="2">
@@ -10601,7 +10752,7 @@
         <v>76</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>78</v>
@@ -10610,23 +10761,19 @@
         <v>78</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>468</v>
+        <v>244</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>469</v>
+        <v>321</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="P79" t="s" s="2">
-        <v>472</v>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="O79" s="2"/>
+      <c r="P79" s="2"/>
       <c r="Q79" t="s" s="2">
         <v>78</v>
       </c>
@@ -10674,41 +10821,41 @@
         <v>78</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>467</v>
+        <v>323</v>
       </c>
       <c r="AH79" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>473</v>
+        <v>432</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>473</v>
+        <v>432</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" t="s" s="2">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="F80" s="2"/>
       <c r="G80" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>78</v>
@@ -10720,18 +10867,18 @@
         <v>78</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>166</v>
+        <v>129</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>474</v>
+        <v>130</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="O80" s="2"/>
-      <c r="P80" t="s" s="2">
-        <v>476</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="P80" s="2"/>
       <c r="Q80" t="s" s="2">
         <v>78</v>
       </c>
@@ -10755,54 +10902,54 @@
         <v>78</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>237</v>
+        <v>78</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>477</v>
+        <v>78</v>
       </c>
       <c r="AA80" t="s" s="2">
-        <v>478</v>
+        <v>78</v>
       </c>
       <c r="AB80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AC80" t="s" s="2">
-        <v>78</v>
+        <v>433</v>
       </c>
       <c r="AD80" t="s" s="2">
-        <v>78</v>
+        <v>434</v>
       </c>
       <c r="AE80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>78</v>
+        <v>435</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>97</v>
+        <v>134</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>479</v>
+        <v>436</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>479</v>
+        <v>436</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" t="s" s="2">
@@ -10819,25 +10966,25 @@
         <v>78</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>480</v>
+        <v>105</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>481</v>
+        <v>437</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>482</v>
+        <v>438</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>483</v>
+        <v>439</v>
       </c>
       <c r="P81" t="s" s="2">
-        <v>484</v>
+        <v>440</v>
       </c>
       <c r="Q81" t="s" s="2">
         <v>78</v>
@@ -10862,13 +11009,13 @@
         <v>78</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>78</v>
+        <v>162</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>78</v>
+        <v>441</v>
       </c>
       <c r="AA81" t="s" s="2">
-        <v>78</v>
+        <v>442</v>
       </c>
       <c r="AB81" t="s" s="2">
         <v>78</v>
@@ -10886,7 +11033,7 @@
         <v>78</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="AH81" t="s" s="2">
         <v>76</v>
@@ -10903,13 +11050,13 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>485</v>
+        <v>444</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>485</v>
+        <v>444</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" t="s" s="2">
@@ -10920,7 +11067,7 @@
         <v>76</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>78</v>
@@ -10929,22 +11076,22 @@
         <v>78</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>486</v>
+        <v>244</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>487</v>
+        <v>445</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>488</v>
+        <v>446</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>489</v>
+        <v>447</v>
       </c>
       <c r="P82" t="s" s="2">
-        <v>490</v>
+        <v>448</v>
       </c>
       <c r="Q82" t="s" s="2">
         <v>78</v>
@@ -10993,13 +11140,13 @@
         <v>78</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>485</v>
+        <v>449</v>
       </c>
       <c r="AH82" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>78</v>
@@ -11010,49 +11157,47 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>491</v>
+        <v>450</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>491</v>
+        <v>450</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" t="s" s="2">
-        <v>78</v>
+        <v>451</v>
       </c>
       <c r="F83" s="2"/>
       <c r="G83" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>279</v>
+        <v>244</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>492</v>
+        <v>452</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>493</v>
+        <v>453</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="P83" t="s" s="2">
-        <v>495</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="P83" s="2"/>
       <c r="Q83" t="s" s="2">
         <v>78</v>
       </c>
@@ -11100,41 +11245,41 @@
         <v>78</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>491</v>
+        <v>455</v>
       </c>
       <c r="AH83" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>496</v>
+        <v>97</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>497</v>
+        <v>456</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>497</v>
+        <v>456</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" t="s" s="2">
-        <v>78</v>
+        <v>457</v>
       </c>
       <c r="F84" s="2"/>
       <c r="G84" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>78</v>
@@ -11143,18 +11288,20 @@
         <v>78</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>286</v>
+        <v>244</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>287</v>
+        <v>458</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="O84" s="2"/>
+        <v>459</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>460</v>
+      </c>
       <c r="P84" s="2"/>
       <c r="Q84" t="s" s="2">
         <v>78</v>
@@ -11203,34 +11350,34 @@
         <v>78</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>289</v>
+        <v>461</v>
       </c>
       <c r="AH84" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>498</v>
+        <v>462</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>498</v>
+        <v>462</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" t="s" s="2">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="F85" s="2"/>
       <c r="G85" t="s" s="2">
@@ -11246,20 +11393,18 @@
         <v>78</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>129</v>
+        <v>244</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>130</v>
+        <v>463</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>132</v>
-      </c>
+        <v>464</v>
+      </c>
+      <c r="O85" s="2"/>
       <c r="P85" s="2"/>
       <c r="Q85" t="s" s="2">
         <v>78</v>
@@ -11308,7 +11453,7 @@
         <v>78</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>292</v>
+        <v>465</v>
       </c>
       <c r="AH85" t="s" s="2">
         <v>76</v>
@@ -11320,22 +11465,22 @@
         <v>78</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>134</v>
+        <v>97</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>499</v>
+        <v>466</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>499</v>
+        <v>466</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" t="s" s="2">
-        <v>294</v>
+        <v>78</v>
       </c>
       <c r="F86" s="2"/>
       <c r="G86" t="s" s="2">
@@ -11348,26 +11493,22 @@
         <v>78</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="K86" t="s" s="2">
         <v>86</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>129</v>
+        <v>244</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>295</v>
+        <v>467</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="P86" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>468</v>
+      </c>
+      <c r="O86" s="2"/>
+      <c r="P86" s="2"/>
       <c r="Q86" t="s" s="2">
         <v>78</v>
       </c>
@@ -11415,7 +11556,7 @@
         <v>78</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>297</v>
+        <v>469</v>
       </c>
       <c r="AH86" t="s" s="2">
         <v>76</v>
@@ -11427,18 +11568,18 @@
         <v>78</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>134</v>
+        <v>97</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>500</v>
+        <v>470</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>500</v>
+        <v>470</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" t="s" s="2">
@@ -11449,7 +11590,7 @@
         <v>76</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>78</v>
@@ -11458,20 +11599,20 @@
         <v>78</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>166</v>
+        <v>214</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>501</v>
+        <v>471</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>502</v>
+        <v>472</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
-        <v>503</v>
+        <v>473</v>
       </c>
       <c r="Q87" t="s" s="2">
         <v>78</v>
@@ -11496,13 +11637,13 @@
         <v>78</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>237</v>
+        <v>78</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>504</v>
+        <v>78</v>
       </c>
       <c r="AA87" t="s" s="2">
-        <v>505</v>
+        <v>78</v>
       </c>
       <c r="AB87" t="s" s="2">
         <v>78</v>
@@ -11520,13 +11661,13 @@
         <v>78</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>500</v>
+        <v>474</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>78</v>
@@ -11537,13 +11678,13 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>506</v>
+        <v>475</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>506</v>
+        <v>475</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" t="s" s="2">
@@ -11554,7 +11695,7 @@
         <v>76</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>78</v>
@@ -11563,20 +11704,22 @@
         <v>78</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>393</v>
+        <v>476</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>507</v>
+        <v>477</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="O88" s="2"/>
+        <v>478</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>479</v>
+      </c>
       <c r="P88" t="s" s="2">
-        <v>509</v>
+        <v>480</v>
       </c>
       <c r="Q88" t="s" s="2">
         <v>78</v>
@@ -11625,13 +11768,13 @@
         <v>78</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>506</v>
+        <v>475</v>
       </c>
       <c r="AH88" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>78</v>
@@ -11642,13 +11785,13 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>510</v>
+        <v>481</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>510</v>
+        <v>481</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" t="s" s="2">
@@ -11659,7 +11802,7 @@
         <v>76</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>78</v>
@@ -11668,22 +11811,22 @@
         <v>78</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>443</v>
+        <v>105</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>511</v>
+        <v>482</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>512</v>
+        <v>483</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>513</v>
+        <v>484</v>
       </c>
       <c r="P89" t="s" s="2">
-        <v>447</v>
+        <v>485</v>
       </c>
       <c r="Q89" t="s" s="2">
         <v>78</v>
@@ -11708,13 +11851,13 @@
         <v>78</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>78</v>
+        <v>162</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>78</v>
+        <v>486</v>
       </c>
       <c r="AA89" t="s" s="2">
-        <v>78</v>
+        <v>487</v>
       </c>
       <c r="AB89" t="s" s="2">
         <v>78</v>
@@ -11732,13 +11875,13 @@
         <v>78</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>510</v>
+        <v>481</v>
       </c>
       <c r="AH89" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>78</v>
@@ -11749,13 +11892,13 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>514</v>
+        <v>488</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>514</v>
+        <v>488</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" t="s" s="2">
@@ -11775,20 +11918,22 @@
         <v>78</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>468</v>
+        <v>489</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>515</v>
+        <v>490</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="O90" s="2"/>
+        <v>491</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>492</v>
+      </c>
       <c r="P90" t="s" s="2">
-        <v>517</v>
+        <v>493</v>
       </c>
       <c r="Q90" t="s" s="2">
         <v>78</v>
@@ -11837,7 +11982,7 @@
         <v>78</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>514</v>
+        <v>488</v>
       </c>
       <c r="AH90" t="s" s="2">
         <v>76</v>
@@ -11854,13 +11999,13 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>518</v>
+        <v>494</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>518</v>
+        <v>494</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" t="s" s="2">
@@ -11877,23 +12022,25 @@
         <v>78</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>105</v>
+        <v>495</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>449</v>
+        <v>496</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="O91" s="2"/>
+        <v>497</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>498</v>
+      </c>
       <c r="P91" t="s" s="2">
-        <v>520</v>
+        <v>499</v>
       </c>
       <c r="Q91" t="s" s="2">
         <v>78</v>
@@ -11918,13 +12065,13 @@
         <v>78</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>162</v>
+        <v>78</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>453</v>
+        <v>78</v>
       </c>
       <c r="AA91" t="s" s="2">
-        <v>454</v>
+        <v>78</v>
       </c>
       <c r="AB91" t="s" s="2">
         <v>78</v>
@@ -11942,7 +12089,7 @@
         <v>78</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>518</v>
+        <v>494</v>
       </c>
       <c r="AH91" t="s" s="2">
         <v>76</v>
@@ -11959,13 +12106,13 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>521</v>
+        <v>500</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>521</v>
+        <v>500</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" t="s" s="2">
@@ -11976,7 +12123,7 @@
         <v>76</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>78</v>
@@ -11985,20 +12132,22 @@
         <v>78</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>522</v>
+        <v>501</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>523</v>
+        <v>502</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="O92" s="2"/>
+        <v>503</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>504</v>
+      </c>
       <c r="P92" t="s" s="2">
-        <v>525</v>
+        <v>505</v>
       </c>
       <c r="Q92" t="s" s="2">
         <v>78</v>
@@ -12047,16 +12196,16 @@
         <v>78</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>521</v>
+        <v>500</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>526</v>
+        <v>78</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>97</v>
@@ -12064,13 +12213,13 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>527</v>
+        <v>506</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>527</v>
+        <v>506</v>
       </c>
       <c r="D93" s="2"/>
       <c r="E93" t="s" s="2">
@@ -12093,16 +12242,18 @@
         <v>78</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>437</v>
+        <v>166</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>528</v>
+        <v>507</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>529</v>
+        <v>508</v>
       </c>
       <c r="O93" s="2"/>
-      <c r="P93" s="2"/>
+      <c r="P93" t="s" s="2">
+        <v>509</v>
+      </c>
       <c r="Q93" t="s" s="2">
         <v>78</v>
       </c>
@@ -12126,13 +12277,13 @@
         <v>78</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>78</v>
+        <v>272</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>78</v>
+        <v>510</v>
       </c>
       <c r="AA93" t="s" s="2">
-        <v>78</v>
+        <v>511</v>
       </c>
       <c r="AB93" t="s" s="2">
         <v>78</v>
@@ -12150,7 +12301,7 @@
         <v>78</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>527</v>
+        <v>506</v>
       </c>
       <c r="AH93" t="s" s="2">
         <v>76</v>
@@ -12167,13 +12318,13 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>530</v>
+        <v>512</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>530</v>
+        <v>512</v>
       </c>
       <c r="D94" s="2"/>
       <c r="E94" t="s" s="2">
@@ -12184,7 +12335,7 @@
         <v>76</v>
       </c>
       <c r="H94" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I94" t="s" s="2">
         <v>78</v>
@@ -12196,19 +12347,19 @@
         <v>78</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>279</v>
+        <v>513</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>531</v>
+        <v>514</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>532</v>
+        <v>515</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>533</v>
+        <v>516</v>
       </c>
       <c r="P94" t="s" s="2">
-        <v>534</v>
+        <v>517</v>
       </c>
       <c r="Q94" t="s" s="2">
         <v>78</v>
@@ -12257,13 +12408,13 @@
         <v>78</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>530</v>
+        <v>512</v>
       </c>
       <c r="AH94" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>78</v>
@@ -12274,13 +12425,13 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>535</v>
+        <v>518</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>535</v>
+        <v>518</v>
       </c>
       <c r="D95" s="2"/>
       <c r="E95" t="s" s="2">
@@ -12291,7 +12442,7 @@
         <v>76</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>78</v>
@@ -12303,16 +12454,20 @@
         <v>78</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>286</v>
+        <v>519</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>287</v>
+        <v>520</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="O95" s="2"/>
-      <c r="P95" s="2"/>
+        <v>521</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="P95" t="s" s="2">
+        <v>523</v>
+      </c>
       <c r="Q95" t="s" s="2">
         <v>78</v>
       </c>
@@ -12360,34 +12515,34 @@
         <v>78</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>289</v>
+        <v>518</v>
       </c>
       <c r="AH95" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>536</v>
+        <v>524</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>536</v>
+        <v>524</v>
       </c>
       <c r="D96" s="2"/>
       <c r="E96" t="s" s="2">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="F96" s="2"/>
       <c r="G96" t="s" s="2">
@@ -12406,18 +12561,20 @@
         <v>78</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>129</v>
+        <v>314</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>130</v>
+        <v>525</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>291</v>
+        <v>526</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="P96" s="2"/>
+        <v>527</v>
+      </c>
+      <c r="P96" t="s" s="2">
+        <v>528</v>
+      </c>
       <c r="Q96" t="s" s="2">
         <v>78</v>
       </c>
@@ -12465,7 +12622,7 @@
         <v>78</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>292</v>
+        <v>524</v>
       </c>
       <c r="AH96" t="s" s="2">
         <v>76</v>
@@ -12477,54 +12634,50 @@
         <v>78</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>134</v>
+        <v>529</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" t="s" s="2">
-        <v>294</v>
+        <v>78</v>
       </c>
       <c r="F97" s="2"/>
       <c r="G97" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>129</v>
+        <v>244</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>295</v>
+        <v>321</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="P97" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="O97" s="2"/>
+      <c r="P97" s="2"/>
       <c r="Q97" t="s" s="2">
         <v>78</v>
       </c>
@@ -12572,41 +12725,41 @@
         <v>78</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>297</v>
+        <v>323</v>
       </c>
       <c r="AH97" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="D98" s="2"/>
       <c r="E98" t="s" s="2">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="F98" s="2"/>
       <c r="G98" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>78</v>
@@ -12618,20 +12771,18 @@
         <v>78</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>166</v>
+        <v>129</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>539</v>
+        <v>130</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>540</v>
+        <v>325</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="P98" t="s" s="2">
-        <v>542</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="P98" s="2"/>
       <c r="Q98" t="s" s="2">
         <v>78</v>
       </c>
@@ -12655,13 +12806,13 @@
         <v>78</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="AA98" t="s" s="2">
-        <v>111</v>
+        <v>78</v>
       </c>
       <c r="AB98" t="s" s="2">
         <v>78</v>
@@ -12679,65 +12830,65 @@
         <v>78</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>538</v>
+        <v>326</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>97</v>
+        <v>134</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>543</v>
+        <v>532</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>543</v>
+        <v>532</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" t="s" s="2">
-        <v>78</v>
+        <v>328</v>
       </c>
       <c r="F99" s="2"/>
       <c r="G99" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I99" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>386</v>
+        <v>129</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>544</v>
+        <v>329</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>545</v>
+        <v>330</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>546</v>
+        <v>132</v>
       </c>
       <c r="P99" t="s" s="2">
-        <v>547</v>
+        <v>138</v>
       </c>
       <c r="Q99" t="s" s="2">
         <v>78</v>
@@ -12786,34 +12937,34 @@
         <v>78</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>543</v>
+        <v>331</v>
       </c>
       <c r="AH99" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>97</v>
+        <v>134</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>548</v>
+        <v>533</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>548</v>
+        <v>533</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" t="s" s="2">
-        <v>549</v>
+        <v>78</v>
       </c>
       <c r="F100" s="2"/>
       <c r="G100" t="s" s="2">
@@ -12832,18 +12983,18 @@
         <v>78</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>550</v>
+        <v>166</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>551</v>
+        <v>534</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="P100" s="2"/>
+        <v>535</v>
+      </c>
+      <c r="O100" s="2"/>
+      <c r="P100" t="s" s="2">
+        <v>536</v>
+      </c>
       <c r="Q100" t="s" s="2">
         <v>78</v>
       </c>
@@ -12867,13 +13018,13 @@
         <v>78</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>78</v>
+        <v>272</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>78</v>
+        <v>537</v>
       </c>
       <c r="AA100" t="s" s="2">
-        <v>78</v>
+        <v>538</v>
       </c>
       <c r="AB100" t="s" s="2">
         <v>78</v>
@@ -12891,7 +13042,7 @@
         <v>78</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>548</v>
+        <v>533</v>
       </c>
       <c r="AH100" t="s" s="2">
         <v>76</v>
@@ -12908,13 +13059,13 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>554</v>
+        <v>539</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>554</v>
+        <v>539</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" t="s" s="2">
@@ -12934,22 +13085,20 @@
         <v>78</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>522</v>
+        <v>426</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>555</v>
+        <v>540</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>557</v>
-      </c>
+        <v>541</v>
+      </c>
+      <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
-        <v>558</v>
+        <v>542</v>
       </c>
       <c r="Q101" t="s" s="2">
         <v>78</v>
@@ -12998,7 +13147,7 @@
         <v>78</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>554</v>
+        <v>539</v>
       </c>
       <c r="AH101" t="s" s="2">
         <v>76</v>
@@ -13015,13 +13164,13 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>559</v>
+        <v>543</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>559</v>
+        <v>543</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" t="s" s="2">
@@ -13038,25 +13187,25 @@
         <v>78</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>279</v>
+        <v>476</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>560</v>
+        <v>544</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>561</v>
+        <v>545</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>562</v>
+        <v>546</v>
       </c>
       <c r="P102" t="s" s="2">
-        <v>563</v>
+        <v>480</v>
       </c>
       <c r="Q102" t="s" s="2">
         <v>78</v>
@@ -13105,7 +13254,7 @@
         <v>78</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>559</v>
+        <v>543</v>
       </c>
       <c r="AH102" t="s" s="2">
         <v>76</v>
@@ -13122,13 +13271,13 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>564</v>
+        <v>547</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>564</v>
+        <v>547</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" t="s" s="2">
@@ -13151,16 +13300,18 @@
         <v>78</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>286</v>
+        <v>501</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>287</v>
+        <v>548</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>288</v>
+        <v>549</v>
       </c>
       <c r="O103" s="2"/>
-      <c r="P103" s="2"/>
+      <c r="P103" t="s" s="2">
+        <v>550</v>
+      </c>
       <c r="Q103" t="s" s="2">
         <v>78</v>
       </c>
@@ -13208,7 +13359,7 @@
         <v>78</v>
       </c>
       <c r="AG103" t="s" s="2">
-        <v>289</v>
+        <v>547</v>
       </c>
       <c r="AH103" t="s" s="2">
         <v>76</v>
@@ -13220,29 +13371,29 @@
         <v>78</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>565</v>
+        <v>551</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>565</v>
+        <v>551</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" t="s" s="2">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="F104" s="2"/>
       <c r="G104" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>78</v>
@@ -13254,18 +13405,18 @@
         <v>78</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>130</v>
+        <v>482</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="P104" s="2"/>
+        <v>552</v>
+      </c>
+      <c r="O104" s="2"/>
+      <c r="P104" t="s" s="2">
+        <v>553</v>
+      </c>
       <c r="Q104" t="s" s="2">
         <v>78</v>
       </c>
@@ -13289,13 +13440,13 @@
         <v>78</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>78</v>
+        <v>162</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>78</v>
+        <v>486</v>
       </c>
       <c r="AA104" t="s" s="2">
-        <v>78</v>
+        <v>487</v>
       </c>
       <c r="AB104" t="s" s="2">
         <v>78</v>
@@ -13313,65 +13464,63 @@
         <v>78</v>
       </c>
       <c r="AG104" t="s" s="2">
-        <v>292</v>
+        <v>551</v>
       </c>
       <c r="AH104" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>134</v>
+        <v>97</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" t="s" s="2">
-        <v>294</v>
+        <v>78</v>
       </c>
       <c r="F105" s="2"/>
       <c r="G105" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H105" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I105" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>129</v>
+        <v>555</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>295</v>
+        <v>556</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>132</v>
-      </c>
+        <v>557</v>
+      </c>
+      <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
-        <v>138</v>
+        <v>558</v>
       </c>
       <c r="Q105" t="s" s="2">
         <v>78</v>
@@ -13420,30 +13569,30 @@
         <v>78</v>
       </c>
       <c r="AG105" t="s" s="2">
-        <v>297</v>
+        <v>554</v>
       </c>
       <c r="AH105" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>78</v>
+        <v>559</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>134</v>
+        <v>97</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
@@ -13451,7 +13600,7 @@
       </c>
       <c r="F106" s="2"/>
       <c r="G106" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>85</v>
@@ -13463,20 +13612,18 @@
         <v>78</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>568</v>
+        <v>214</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>571</v>
-      </c>
+        <v>562</v>
+      </c>
+      <c r="O106" s="2"/>
       <c r="P106" s="2"/>
       <c r="Q106" t="s" s="2">
         <v>78</v>
@@ -13525,10 +13672,10 @@
         <v>78</v>
       </c>
       <c r="AG106" t="s" s="2">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>85</v>
@@ -13542,13 +13689,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>572</v>
+        <v>563</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>572</v>
+        <v>563</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
@@ -13556,10 +13703,10 @@
       </c>
       <c r="F107" s="2"/>
       <c r="G107" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H107" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I107" t="s" s="2">
         <v>78</v>
@@ -13568,19 +13715,23 @@
         <v>78</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>105</v>
+        <v>314</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="O107" s="2"/>
-      <c r="P107" s="2"/>
+        <v>565</v>
+      </c>
+      <c r="O107" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="P107" t="s" s="2">
+        <v>567</v>
+      </c>
       <c r="Q107" t="s" s="2">
         <v>78</v>
       </c>
@@ -13604,42 +13755,1413 @@
         <v>78</v>
       </c>
       <c r="Y107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="C108" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="D108" s="2"/>
+      <c r="E108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F108" s="2"/>
+      <c r="G108" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="O108" s="2"/>
+      <c r="P108" s="2"/>
+      <c r="Q108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R108" s="2"/>
+      <c r="S108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI108" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="C109" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="D109" s="2"/>
+      <c r="E109" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="F109" s="2"/>
+      <c r="G109" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="O109" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="P109" s="2"/>
+      <c r="Q109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R109" s="2"/>
+      <c r="S109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG109" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AH109" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="C110" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="D110" s="2"/>
+      <c r="E110" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="F110" s="2"/>
+      <c r="G110" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J110" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="K110" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="O110" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="P110" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="Q110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R110" s="2"/>
+      <c r="S110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG110" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AH110" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK110" t="s" s="2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="C111" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="D111" s="2"/>
+      <c r="E111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F111" s="2"/>
+      <c r="G111" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H111" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="O111" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="P111" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="Q111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R111" s="2"/>
+      <c r="S111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="Z111" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG111" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AH111" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI111" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK111" t="s" s="2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="C112" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="D112" s="2"/>
+      <c r="E112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F112" s="2"/>
+      <c r="G112" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="O112" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="P112" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="Q112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R112" s="2"/>
+      <c r="S112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG112" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="AH112" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI112" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="C113" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="D113" s="2"/>
+      <c r="E113" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="F113" s="2"/>
+      <c r="G113" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="O113" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="P113" s="2"/>
+      <c r="Q113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R113" s="2"/>
+      <c r="S113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG113" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AH113" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK113" t="s" s="2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="C114" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="D114" s="2"/>
+      <c r="E114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F114" s="2"/>
+      <c r="G114" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="O114" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="P114" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="Q114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R114" s="2"/>
+      <c r="S114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK114" t="s" s="2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="C115" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="D115" s="2"/>
+      <c r="E115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F115" s="2"/>
+      <c r="G115" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J115" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="K115" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="O115" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="P115" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="Q115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R115" s="2"/>
+      <c r="S115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG115" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="AH115" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK115" t="s" s="2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="C116" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="D116" s="2"/>
+      <c r="E116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F116" s="2"/>
+      <c r="G116" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H116" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="O116" s="2"/>
+      <c r="P116" s="2"/>
+      <c r="Q116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R116" s="2"/>
+      <c r="S116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG116" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AH116" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI116" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK116" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="C117" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="D117" s="2"/>
+      <c r="E117" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="F117" s="2"/>
+      <c r="G117" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="O117" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="P117" s="2"/>
+      <c r="Q117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R117" s="2"/>
+      <c r="S117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG117" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AH117" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK117" t="s" s="2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="C118" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="D118" s="2"/>
+      <c r="E118" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="F118" s="2"/>
+      <c r="G118" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J118" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="K118" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L118" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="M118" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="O118" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="P118" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="Q118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R118" s="2"/>
+      <c r="S118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG118" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AH118" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK118" t="s" s="2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="C119" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="D119" s="2"/>
+      <c r="E119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F119" s="2"/>
+      <c r="G119" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H119" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K119" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L119" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="M119" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="O119" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="P119" s="2"/>
+      <c r="Q119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R119" s="2"/>
+      <c r="S119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG119" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AH119" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI119" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK119" t="s" s="2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="C120" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="D120" s="2"/>
+      <c r="E120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F120" s="2"/>
+      <c r="G120" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H120" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K120" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L120" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M120" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="O120" s="2"/>
+      <c r="P120" s="2"/>
+      <c r="Q120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R120" s="2"/>
+      <c r="S120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y120" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="Z107" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="AA107" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="AB107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AG107" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="AH107" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI107" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK107" t="s" s="2">
+      <c r="Z120" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG120" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="AH120" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI120" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK120" t="s" s="2">
         <v>97</v>
       </c>
     </row>

--- a/currentbuild/all-profiles.xlsx
+++ b/currentbuild/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.4.2</t>
+    <t>1.4.3</t>
   </si>
   <si>
     <t>Name</t>

--- a/currentbuild/all-profiles.xlsx
+++ b/currentbuild/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.4.3</t>
+    <t>1.4.4</t>
   </si>
   <si>
     <t>Name</t>

--- a/currentbuild/all-profiles.xlsx
+++ b/currentbuild/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.4.5</t>
+    <t>1.4.6</t>
   </si>
   <si>
     <t>Name</t>

--- a/currentbuild/all-profiles.xlsx
+++ b/currentbuild/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.4.6</t>
+    <t>1.4.7</t>
   </si>
   <si>
     <t>Name</t>
